--- a/sheets/민요/검수/풍년가-2.xlsx
+++ b/sheets/민요/검수/풍년가-2.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/풍년가-2.xlsx
+++ b/sheets/민요/검수/풍년가-2.xlsx
@@ -4184,6 +4184,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4204,10 +4207,10 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="52.21" customHeight="1">
+    <row r="2" ht="68.97" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4230,7 +4233,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="52.21" customHeight="1">
+    <row r="3" ht="102.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4313,7 +4316,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52.21" customHeight="1">
+    <row r="4" ht="102.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4380,7 +4383,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="52.21" customHeight="1">
+    <row r="5" ht="102.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4431,7 +4434,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="52.21" customHeight="1">
+    <row r="6" ht="102.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4508,7 +4511,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52.21" customHeight="1">
+    <row r="7" ht="102.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4575,7 +4578,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="52.21" customHeight="1">
+    <row r="8" ht="102.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4648,7 +4651,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52.21" customHeight="1">
+    <row r="9" ht="102.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4731,7 +4734,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52.21" customHeight="1">
+    <row r="10" ht="102.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4798,7 +4801,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="52.21" customHeight="1">
+    <row r="11" ht="102.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4860,7 +4863,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="52.21" customHeight="1">
+    <row r="12" ht="102.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4939,7 +4942,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52.21" customHeight="1">
+    <row r="13" ht="102.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5002,7 +5005,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="52.21" customHeight="1">
+    <row r="14" ht="102.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5073,6 +5076,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/풍년가-2.xlsx
+++ b/sheets/민요/검수/풍년가-2.xlsx
@@ -4189,28 +4189,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="68.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="102.71" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="102.71" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="102.71" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="102.71" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="102.71" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="102.71" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="102.71" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="102.71" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="102.71" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="102.71" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="102.71" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="102.71" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5076,6 +5076,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>